--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0665891170501709</v>
+        <v>0.08849072456359863</v>
       </c>
       <c r="E2" t="n">
         <v>0.9961400709277428</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08024287223815918</v>
+        <v>0.09751772880554199</v>
       </c>
       <c r="E3" t="n">
         <v>0.9978228952075805</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0665891170501709</v>
+        <v>0.08849072456359863</v>
       </c>
       <c r="E2" t="n">
         <v>0.9961400709277428</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08024287223815918</v>
+        <v>0.09751772880554199</v>
       </c>
       <c r="E3" t="n">
         <v>0.9978228952075805</v>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08849072456359863</v>
+        <v>7.384719848632812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9961400709277428</v>
+        <v>0.9956186096202421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9991937940340722</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5595412624943363</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4184629446750223</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,93 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09751772880554199</v>
+        <v>5.618981122970581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9978228952075805</v>
+        <v>0.996369932630607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9991937940340722</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5595412624943363</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4184629446750223</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.586958169937134</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9966415254415318</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.590544462203979</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9967493472834448</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +627,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +692,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08849072456359863</v>
+        <v>7.384719848632812</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9961400709277428</v>
+        <v>0.9956186096202421</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9991937940340722</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5595412624943363</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4184629446750223</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +727,93 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09751772880554199</v>
+        <v>5.618981122970581</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9978228952075805</v>
+        <v>0.996369932630607</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9991937940340722</v>
+        <v>0.9968511658570547</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5595412624943363</v>
+        <v>9.985445827134786</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4184629446750223</v>
+        <v>6.516757399697644</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>6.586958169937134</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9966415254415318</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G4" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H4" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>15</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6.590544462203979</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9967493472834448</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9968511658570547</v>
+      </c>
+      <c r="G5" t="n">
+        <v>9.985445827134786</v>
+      </c>
+      <c r="H5" t="n">
+        <v>6.516757399697644</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.384719848632812</v>
+        <v>4.127224206924438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9956186096202421</v>
+        <v>0.9962548380768484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G2" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.618981122970581</v>
+        <v>2.992775201797485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.996369932630607</v>
+        <v>0.9970077248654106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G3" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H3" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -561,23 +561,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.586958169937134</v>
+        <v>3.482832908630371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966415254415318</v>
+        <v>0.9973717366034205</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G4" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H4" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>6.590544462203979</v>
+        <v>3.67577338218689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967493472834448</v>
+        <v>0.9974269041414209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G5" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H5" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -692,23 +692,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>7.384719848632812</v>
+        <v>4.127224206924438</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9956186096202421</v>
+        <v>0.9962548380768484</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G2" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H2" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -727,23 +727,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.618981122970581</v>
+        <v>2.992775201797485</v>
       </c>
       <c r="E3" t="n">
-        <v>0.996369932630607</v>
+        <v>0.9970077248654106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G3" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H3" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -762,23 +762,23 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>6.586958169937134</v>
+        <v>3.482832908630371</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9966415254415318</v>
+        <v>0.9973717366034205</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G4" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H4" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -797,23 +797,23 @@
         <v>15</v>
       </c>
       <c r="D5" t="n">
-        <v>6.590544462203979</v>
+        <v>3.67577338218689</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9967493472834448</v>
+        <v>0.9974269041414209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9968511658570547</v>
+        <v>0.9974665152819624</v>
       </c>
       <c r="G5" t="n">
-        <v>9.985445827134786</v>
+        <v>8.956775966344631</v>
       </c>
       <c r="H5" t="n">
-        <v>6.516757399697644</v>
+        <v>5.924799097085533</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.127224206924438</v>
+        <v>0.1729857921600342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.992775201797485</v>
+        <v>0.1327650547027588</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.482832908630371</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9973717366034205</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.67577338218689</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>4.127224206924438</v>
+        <v>0.1729857921600342</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9962548380768484</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.992775201797485</v>
+        <v>0.1327650547027588</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9970077248654106</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9974665152819624</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>8.956775966344631</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>5.924799097085533</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>3.482832908630371</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9973717366034205</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G4" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H4" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.67577338218689</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9974269041414209</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.9974665152819624</v>
-      </c>
-      <c r="G5" t="n">
-        <v>8.956775966344631</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.924799097085533</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 5, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1729857921600342</v>
+        <v>5.239706039428711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.5814725452298296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.7617427573423822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.117597323689839</v>
+        <v>86.85915952070602</v>
       </c>
       <c r="H2" t="n">
-        <v>3.150367965367966</v>
+        <v>54.41030089618448</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327650547027588</v>
+        <v>5.04226016998291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.6631154743275178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.7617427573423822</v>
       </c>
       <c r="G3" t="n">
-        <v>4.117597323689839</v>
+        <v>86.85915952070602</v>
       </c>
       <c r="H3" t="n">
-        <v>3.150367965367966</v>
+        <v>54.41030089618448</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.686679124832153</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7092556566463324</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7617427573423822</v>
+      </c>
+      <c r="G4" t="n">
+        <v>86.85915952070602</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54.41030089618448</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1729857921600342</v>
+        <v>5.239706039428711</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.5814725452298296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.7617427573423822</v>
       </c>
       <c r="G2" t="n">
-        <v>4.117597323689839</v>
+        <v>86.85915952070602</v>
       </c>
       <c r="H2" t="n">
-        <v>3.150367965367966</v>
+        <v>54.41030089618448</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1327650547027588</v>
+        <v>5.04226016998291</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.6631154743275178</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.7617427573423822</v>
       </c>
       <c r="G3" t="n">
-        <v>4.117597323689839</v>
+        <v>86.85915952070602</v>
       </c>
       <c r="H3" t="n">
-        <v>3.150367965367966</v>
+        <v>54.41030089618448</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>5.686679124832153</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.7092556566463324</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.7617427573423822</v>
+      </c>
+      <c r="G4" t="n">
+        <v>86.85915952070602</v>
+      </c>
+      <c r="H4" t="n">
+        <v>54.41030089618448</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.239706039428711</v>
+        <v>0.1228775978088379</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5814725452298296</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7617427573423822</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>86.85915952070602</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>54.41030089618448</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.04226016998291</v>
+        <v>0.08171677589416504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6631154743275178</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7617427573423822</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>86.85915952070602</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>54.41030089618448</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.686679124832153</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7092556566463324</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7617427573423822</v>
-      </c>
-      <c r="G4" t="n">
-        <v>86.85915952070602</v>
-      </c>
-      <c r="H4" t="n">
-        <v>54.41030089618448</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>5.239706039428711</v>
+        <v>0.1228775978088379</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5814725452298296</v>
+        <v>0.9500806472555414</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7617427573423822</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G2" t="n">
-        <v>86.85915952070602</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H2" t="n">
-        <v>54.41030089618448</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>5.04226016998291</v>
+        <v>0.08171677589416504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6631154743275178</v>
+        <v>0.9586722896604414</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7617427573423822</v>
+        <v>0.9563414289885007</v>
       </c>
       <c r="G3" t="n">
-        <v>86.85915952070602</v>
+        <v>4.117597323689839</v>
       </c>
       <c r="H3" t="n">
-        <v>54.41030089618448</v>
+        <v>3.150367965367966</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>5.686679124832153</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.7092556566463324</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.7617427573423822</v>
-      </c>
-      <c r="G4" t="n">
-        <v>86.85915952070602</v>
-      </c>
-      <c r="H4" t="n">
-        <v>54.41030089618448</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1228775978088379</v>
+        <v>0.1230432987213135</v>
       </c>
       <c r="E2" t="n">
         <v>0.9500806472555414</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08171677589416504</v>
+        <v>0.08407974243164062</v>
       </c>
       <c r="E3" t="n">
         <v>0.9586722896604414</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1228775978088379</v>
+        <v>0.1230432987213135</v>
       </c>
       <c r="E2" t="n">
         <v>0.9500806472555414</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08171677589416504</v>
+        <v>0.08407974243164062</v>
       </c>
       <c r="E3" t="n">
         <v>0.9586722896604414</v>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1230432987213135</v>
+        <v>0.1091556549072266</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>4.117597323689839</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>3.150367965367966</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08407974243164062</v>
+        <v>0.07182192802429199</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>4.117597323689839</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>3.150367965367966</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1230432987213135</v>
+        <v>0.1091556549072266</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9500806472555414</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>4.117597323689839</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>3.150367965367966</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.08407974243164062</v>
+        <v>0.07182192802429199</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9586722896604414</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9563414289885007</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>4.117597323689839</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>3.150367965367966</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'uniform'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1091556549072266</v>
+        <v>30.03185176849365</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07182192802429199</v>
+        <v>27.93966317176819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1091556549072266</v>
+        <v>30.03185176849365</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.07182192802429199</v>
+        <v>27.93966317176819</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 3, 'weights': 'distance'}</t>
+          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.03185176849365</v>
+        <v>0.04735612869262695</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.93966317176819</v>
+        <v>0.05784749984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>30.03185176849365</v>
+        <v>0.04735612869262695</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>27.93966317176819</v>
+        <v>0.05784749984741211</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'euclidean', 'n_neighbors': 7, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04735612869262695</v>
+        <v>12.3324511051178</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.5765101226696233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05784749984741211</v>
+        <v>14.35354351997375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.5896721788986901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.04735612869262695</v>
+        <v>12.3324511051178</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.5765101226696233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.05784749984741211</v>
+        <v>14.35354351997375</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.5896721788986901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3324511051178</v>
+        <v>0.4088060855865479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G2" t="n">
-        <v>109.8546514923718</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H2" t="n">
-        <v>77.9838465335159</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,19 +526,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.35354351997375</v>
+        <v>0.4109337329864502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G3" t="n">
-        <v>109.8546514923718</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H3" t="n">
-        <v>77.9838465335159</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.3324511051178</v>
+        <v>0.4088060855865479</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G2" t="n">
-        <v>109.8546514923718</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H2" t="n">
-        <v>77.9838465335159</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,19 +657,19 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.35354351997375</v>
+        <v>0.4109337329864502</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G3" t="n">
-        <v>109.8546514923718</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H3" t="n">
-        <v>77.9838465335159</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4088060855865479</v>
+        <v>3.815935373306274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593756937122587</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3799547808937107</v>
+        <v>29.24887821574554</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4109337329864502</v>
+        <v>4.348508358001709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.593756937122587</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3799547808937107</v>
+        <v>27.77407416552622</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4088060855865479</v>
+        <v>3.815935373306274</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593756937122587</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3799547808937107</v>
+        <v>29.24887821574554</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4109337329864502</v>
+        <v>4.348508358001709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.593756937122587</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3799547808937107</v>
+        <v>27.77407416552622</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.815935373306274</v>
+        <v>0.05839180946350098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>64.25814371519127</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>29.24887821574554</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,21 +526,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.348508358001709</v>
+        <v>0.1200497150421143</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>62.98221635411645</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>27.77407416552622</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1213326454162598</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.815935373306274</v>
+        <v>0.05839180946350098</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>64.25814371519127</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>29.24887821574554</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,21 +692,56 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.348508358001709</v>
+        <v>0.1200497150421143</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>62.98221635411645</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>27.77407416552622</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1213326454162598</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05839180946350098</v>
+        <v>2.125401735305786</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.5765101226696233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1200497150421143</v>
+        <v>2.494043350219727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.5896721788986901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1213326454162598</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.05839180946350098</v>
+        <v>2.125401735305786</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.5765101226696233</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1200497150421143</v>
+        <v>2.494043350219727</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.5896721788986901</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.6188887513166017</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>109.8546514923718</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>77.9838465335159</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1213326454162598</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.125401735305786</v>
+        <v>22.92759561538696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G2" t="n">
-        <v>109.8546514923718</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H2" t="n">
-        <v>77.9838465335159</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.494043350219727</v>
+        <v>22.38435125350952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G3" t="n">
-        <v>109.8546514923718</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H3" t="n">
-        <v>77.9838465335159</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>2.125401735305786</v>
+        <v>22.92759561538696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5765101226696233</v>
+        <v>0.9940702304082292</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G2" t="n">
-        <v>109.8546514923718</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H2" t="n">
-        <v>77.9838465335159</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.494043350219727</v>
+        <v>22.38435125350952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5896721788986901</v>
+        <v>0.9947256554325836</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6188887513166017</v>
+        <v>0.9955557535720156</v>
       </c>
       <c r="G3" t="n">
-        <v>109.8546514923718</v>
+        <v>0.6399832259487974</v>
       </c>
       <c r="H3" t="n">
-        <v>77.9838465335159</v>
+        <v>0.4629059086032067</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 15, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92759561538696</v>
+        <v>3.681244850158691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>29.24887821574554</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22.38435125350952</v>
+        <v>4.550774812698364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>27.77407416552622</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>22.92759561538696</v>
+        <v>3.681244850158691</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9940702304082292</v>
+        <v>0.4935003325207741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.5873816881539017</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6399832259487974</v>
+        <v>64.25814371519127</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4629059086032067</v>
+        <v>29.24887821574554</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>22.38435125350952</v>
+        <v>4.550774812698364</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9947256554325836</v>
+        <v>0.5309137658627969</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9955557535720156</v>
+        <v>0.6036051296434839</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6399832259487974</v>
+        <v>62.98221635411645</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4629059086032067</v>
+        <v>27.77407416552622</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,19 +491,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.681244850158691</v>
+        <v>9.408438682556152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9029883463751035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="G2" t="n">
-        <v>64.25814371519127</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="H2" t="n">
-        <v>29.24887821574554</v>
+        <v>5.22191277459623</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.550774812698364</v>
+        <v>11.40788674354553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9080335763132791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="G3" t="n">
-        <v>62.98221635411645</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="H3" t="n">
-        <v>27.77407416552622</v>
+        <v>5.22191277459623</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -622,19 +622,19 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>3.681244850158691</v>
+        <v>9.408438682556152</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4935003325207741</v>
+        <v>0.9029883463751035</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5873816881539017</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="G2" t="n">
-        <v>64.25814371519127</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="H2" t="n">
-        <v>29.24887821574554</v>
+        <v>5.22191277459623</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>4.550774812698364</v>
+        <v>11.40788674354553</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5309137658627969</v>
+        <v>0.9080335763132791</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6036051296434839</v>
+        <v>0.9210421468734596</v>
       </c>
       <c r="G3" t="n">
-        <v>62.98221635411645</v>
+        <v>9.533459047908195</v>
       </c>
       <c r="H3" t="n">
-        <v>27.77407416552622</v>
+        <v>5.22191277459623</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.408438682556152</v>
+        <v>0.4648361206054688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9029883463751035</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G2" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H2" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.40788674354553</v>
+        <v>0.5001530647277832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9080335763132791</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G3" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H3" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -622,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>9.408438682556152</v>
+        <v>0.4648361206054688</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9029883463751035</v>
+        <v>0.4611791357184896</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G2" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H2" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>11.40788674354553</v>
+        <v>0.5001530647277832</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9080335763132791</v>
+        <v>0.4869014791301536</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9210421468734596</v>
+        <v>0.5447907953088442</v>
       </c>
       <c r="G3" t="n">
-        <v>9.533459047908195</v>
+        <v>0.593756937122587</v>
       </c>
       <c r="H3" t="n">
-        <v>5.22191277459623</v>
+        <v>0.3799547808937107</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 5, 'metric': 'manhattan'}</t>
+          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4648361206054688</v>
+        <v>0.07330489158630371</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593756937122587</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3799547808937107</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -526,23 +526,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5001530647277832</v>
+        <v>0.09761977195739746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.593756937122587</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3799547808937107</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1243677139282227</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -622,23 +657,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4648361206054688</v>
+        <v>0.07330489158630371</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4611791357184896</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.593756937122587</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3799547808937107</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -657,23 +692,58 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5001530647277832</v>
+        <v>0.09761977195739746</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4869014791301536</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5447907953088442</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>0.593756937122587</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3799547808937107</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'metric': 'manhattan', 'n_neighbors': 15, 'weights': 'distance'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1243677139282227</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07330489158630371</v>
+        <v>0.1098024845123291</v>
       </c>
       <c r="E2" t="n">
         <v>0.9753267773098955</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09761977195739746</v>
+        <v>0.09252500534057617</v>
       </c>
       <c r="E3" t="n">
         <v>0.9809646707133171</v>
@@ -561,7 +561,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1243677139282227</v>
+        <v>0.1617021560668945</v>
       </c>
       <c r="E4" t="n">
         <v>0.9829335526451433</v>
@@ -657,7 +657,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.07330489158630371</v>
+        <v>0.1098024845123291</v>
       </c>
       <c r="E2" t="n">
         <v>0.9753267773098955</v>
@@ -692,7 +692,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09761977195739746</v>
+        <v>0.09252500534057617</v>
       </c>
       <c r="E3" t="n">
         <v>0.9809646707133171</v>
@@ -727,7 +727,7 @@
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1243677139282227</v>
+        <v>0.1617021560668945</v>
       </c>
       <c r="E4" t="n">
         <v>0.9829335526451433</v>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1098024845123291</v>
+        <v>1.562232732772827</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.6182642045857853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -523,61 +523,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09252500534057617</v>
+        <v>2.088099718093872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.6218922072306379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1617021560668945</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,26 +619,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1098024845123291</v>
+        <v>1.562232732772827</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.6182642045857853</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -689,61 +654,26 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09252500534057617</v>
+        <v>2.088099718093872</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.6218922072306379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.610371309728729</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>83.24998363278404</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>58.25620790008099</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1617021560668945</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,26 +488,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.562232732772827</v>
+        <v>0.08384418487548828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6182642045857853</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.610371309728729</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>83.24998363278404</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>58.25620790008099</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -523,26 +523,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.088099718093872</v>
+        <v>0.1074974536895752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6218922072306379</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.610371309728729</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>83.24998363278404</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>58.25620790008099</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1651961803436279</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -557,7 +592,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,26 +654,26 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>1.562232732772827</v>
+        <v>0.08384418487548828</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6182642045857853</v>
+        <v>0.9753267773098955</v>
       </c>
       <c r="F2" t="n">
-        <v>0.610371309728729</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G2" t="n">
-        <v>83.24998363278404</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H2" t="n">
-        <v>58.25620790008099</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>
@@ -654,26 +689,61 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>2.088099718093872</v>
+        <v>0.1074974536895752</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6218922072306379</v>
+        <v>0.9809646707133171</v>
       </c>
       <c r="F3" t="n">
-        <v>0.610371309728729</v>
+        <v>0.9907000428793515</v>
       </c>
       <c r="G3" t="n">
-        <v>83.24998363278404</v>
+        <v>1.9004199798826</v>
       </c>
       <c r="H3" t="n">
-        <v>58.25620790008099</v>
+        <v>1.388601264472551</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 11, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>10</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.1651961803436279</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9829335526451433</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.9907000428793515</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.9004199798826</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.388601264472551</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08384418487548828</v>
+        <v>12.45971918106079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.989567395589308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -526,58 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1074974536895752</v>
+        <v>14.872154712677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.9904880707374442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1651961803436279</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -592,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -657,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>0.08384418487548828</v>
+        <v>12.45971918106079</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9753267773098955</v>
+        <v>0.989567395589308</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G2" t="n">
-        <v>1.9004199798826</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H2" t="n">
-        <v>1.388601264472551</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>
@@ -692,58 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1074974536895752</v>
+        <v>14.872154712677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9809646707133171</v>
+        <v>0.9904880707374442</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9907000428793515</v>
+        <v>0.9913454450269565</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9004199798826</v>
+        <v>0.8821995297482219</v>
       </c>
       <c r="H3" t="n">
-        <v>1.388601264472551</v>
+        <v>0.6634157895241657</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.1651961803436279</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9829335526451433</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.9907000428793515</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.9004199798826</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1.388601264472551</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'weights': 'distance', 'n_neighbors': 3, 'metric': 'manhattan'}</t>
+          <t>{'weights': 'distance', 'n_neighbors': 7, 'metric': 'euclidean'}</t>
         </is>
       </c>
     </row>

--- a/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
+++ b/output/reports/cv_experiment_KNN_kmeans_regression.xlsx
@@ -491,7 +491,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.45971918106079</v>
+        <v>11.81552910804749</v>
       </c>
       <c r="E2" t="n">
         <v>0.989567395589308</v>
@@ -526,7 +526,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.872154712677</v>
+        <v>15.45020747184753</v>
       </c>
       <c r="E3" t="n">
         <v>0.9904880707374442</v>
@@ -622,7 +622,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>12.45971918106079</v>
+        <v>11.81552910804749</v>
       </c>
       <c r="E2" t="n">
         <v>0.989567395589308</v>
@@ -657,7 +657,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>14.872154712677</v>
+        <v>15.45020747184753</v>
       </c>
       <c r="E3" t="n">
         <v>0.9904880707374442</v>
